--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -496,27 +496,27 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>5_star_count</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>4_star_count</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>3_star_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2_star_count</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>1_star_count</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>2_star_count</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>3_star_count</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>4_star_count</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>5_star_count</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:13</t>
+          <t>2026-05-22 17:42:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -577,19 +577,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:13</t>
+          <t>2026-05-22 17:42:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81996</v>
+        <v>4.81974</v>
       </c>
       <c r="G3" t="n">
-        <v>12392</v>
+        <v>12399</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>11531</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:13</t>
+          <t>2026-05-22 17:42:05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -721,19 +721,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2959</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>955</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:14</t>
+          <t>2026-05-22 17:42:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.53683</v>
+        <v>2.53619</v>
       </c>
       <c r="G5" t="n">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>769</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:14</t>
+          <t>2026-05-22 17:42:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:14</t>
+          <t>2026-05-22 17:42:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.02043</v>
+        <v>4.01959</v>
       </c>
       <c r="G7" t="n">
-        <v>3622</v>
+        <v>3623</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2319</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>399</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:14</t>
+          <t>2026-05-22 17:42:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74871</v>
+        <v>4.74855</v>
       </c>
       <c r="G8" t="n">
-        <v>13140</v>
+        <v>13148</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,19 +1009,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>11833</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>526</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>526</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:14</t>
+          <t>2026-05-22 17:42:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>624</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:14</t>
+          <t>2026-05-22 17:42:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,19 +1153,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:14</t>
+          <t>2026-05-22 17:42:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:14</t>
+          <t>2026-05-22 17:42:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74498</v>
+        <v>4.74535</v>
       </c>
       <c r="G12" t="n">
-        <v>2843</v>
+        <v>2847</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,19 +1297,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2505</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:14</t>
+          <t>2026-05-22 17:42:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1369,19 +1369,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:15</t>
+          <t>2026-05-22 17:42:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1441,19 +1441,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:15</t>
+          <t>2026-05-22 17:42:23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:15</t>
+          <t>2026-05-22 17:42:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.75</v>
+        <v>4.75005</v>
       </c>
       <c r="G16" t="n">
-        <v>31077</v>
+        <v>31082</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>27663</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1243</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>622</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1243</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -496,27 +496,27 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>1_star_count</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>2_star_count</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>3_star_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>4_star_count</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>5_star_count</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>4_star_count</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>3_star_count</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>2_star_count</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>1_star_count</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 17:42:02</t>
+          <t>2026-05-22 18:26:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -577,19 +577,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-22 17:42:03</t>
+          <t>2026-05-22 18:26:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11531</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>372</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22 17:42:05</t>
+          <t>2026-05-22 18:27:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -721,19 +721,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2959</v>
+        <v>955</v>
       </c>
       <c r="O4" t="n">
-        <v>382</v>
+        <v>239</v>
       </c>
       <c r="P4" t="n">
         <v>239</v>
       </c>
       <c r="Q4" t="n">
-        <v>239</v>
+        <v>382</v>
       </c>
       <c r="R4" t="n">
-        <v>955</v>
+        <v>2959</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-22 17:42:07</t>
+          <t>2026-05-22 18:27:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>769</v>
+        <v>1298</v>
       </c>
       <c r="O5" t="n">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="P5" t="n">
         <v>96</v>
       </c>
       <c r="Q5" t="n">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="R5" t="n">
-        <v>1298</v>
+        <v>769</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-22 17:42:08</t>
+          <t>2026-05-22 18:27:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="O6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="P6" t="n">
         <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="R6" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-22 17:42:10</t>
+          <t>2026-05-22 18:27:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2319</v>
+        <v>580</v>
       </c>
       <c r="O7" t="n">
-        <v>399</v>
+        <v>145</v>
       </c>
       <c r="P7" t="n">
         <v>181</v>
       </c>
       <c r="Q7" t="n">
-        <v>145</v>
+        <v>399</v>
       </c>
       <c r="R7" t="n">
-        <v>580</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-22 17:42:12</t>
+          <t>2026-05-22 18:27:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1009,19 +1009,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>11833</v>
+        <v>526</v>
       </c>
       <c r="O8" t="n">
-        <v>526</v>
+        <v>131</v>
       </c>
       <c r="P8" t="n">
         <v>263</v>
       </c>
       <c r="Q8" t="n">
-        <v>131</v>
+        <v>526</v>
       </c>
       <c r="R8" t="n">
-        <v>526</v>
+        <v>11833</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-22 17:42:13</t>
+          <t>2026-05-22 18:27:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>624</v>
+        <v>50</v>
       </c>
       <c r="O9" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="P9" t="n">
         <v>7</v>
       </c>
       <c r="Q9" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="R9" t="n">
-        <v>50</v>
+        <v>624</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-22 17:42:15</t>
+          <t>2026-05-22 18:27:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,19 +1153,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>650</v>
+        <v>224</v>
       </c>
       <c r="O10" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="P10" t="n">
         <v>41</v>
       </c>
       <c r="Q10" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="R10" t="n">
-        <v>224</v>
+        <v>650</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-22 17:42:17</t>
+          <t>2026-05-22 18:27:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1225,19 +1225,19 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>13</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
         <v>11</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-22 17:42:18</t>
+          <t>2026-05-22 18:27:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1297,19 +1297,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2505</v>
+        <v>85</v>
       </c>
       <c r="O12" t="n">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="P12" t="n">
         <v>57</v>
       </c>
       <c r="Q12" t="n">
-        <v>28</v>
+        <v>142</v>
       </c>
       <c r="R12" t="n">
-        <v>85</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-22 17:42:20</t>
+          <t>2026-05-22 18:27:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1369,19 +1369,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>357</v>
+        <v>98</v>
       </c>
       <c r="O13" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="P13" t="n">
         <v>16</v>
       </c>
       <c r="Q13" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="R13" t="n">
-        <v>98</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-22 17:42:21</t>
+          <t>2026-05-22 18:27:16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1441,19 +1441,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
         <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>85</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-22 17:42:23</t>
+          <t>2026-05-22 18:27:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1525,7 +1525,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-22 17:42:24</t>
+          <t>2026-05-22 18:27:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>27663</v>
+        <v>1243</v>
       </c>
       <c r="O16" t="n">
-        <v>1243</v>
+        <v>311</v>
       </c>
       <c r="P16" t="n">
         <v>622</v>
       </c>
       <c r="Q16" t="n">
-        <v>311</v>
+        <v>1243</v>
       </c>
       <c r="R16" t="n">
-        <v>1243</v>
+        <v>27663</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -496,27 +496,27 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>5_star_count</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>4_star_count</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>3_star_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2_star_count</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>1_star_count</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>2_star_count</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>3_star_count</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>4_star_count</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>5_star_count</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 18:26:58</t>
+          <t>2026-05-22 18:51:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -577,19 +577,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-22 18:26:59</t>
+          <t>2026-05-22 18:51:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>11531</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22 18:27:00</t>
+          <t>2026-05-22 18:51:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -721,19 +721,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>955</v>
+        <v>2959</v>
       </c>
       <c r="O4" t="n">
-        <v>239</v>
+        <v>382</v>
       </c>
       <c r="P4" t="n">
         <v>239</v>
       </c>
       <c r="Q4" t="n">
-        <v>382</v>
+        <v>239</v>
       </c>
       <c r="R4" t="n">
-        <v>2959</v>
+        <v>955</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-22 18:27:02</t>
+          <t>2026-05-22 18:51:35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1298</v>
+        <v>769</v>
       </c>
       <c r="O5" t="n">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="P5" t="n">
         <v>96</v>
       </c>
       <c r="Q5" t="n">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="R5" t="n">
-        <v>769</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-22 18:27:04</t>
+          <t>2026-05-22 18:51:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="O6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P6" t="n">
         <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="R6" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-22 18:27:05</t>
+          <t>2026-05-22 18:51:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>580</v>
+        <v>2319</v>
       </c>
       <c r="O7" t="n">
-        <v>145</v>
+        <v>399</v>
       </c>
       <c r="P7" t="n">
         <v>181</v>
       </c>
       <c r="Q7" t="n">
-        <v>399</v>
+        <v>145</v>
       </c>
       <c r="R7" t="n">
-        <v>2319</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-22 18:27:07</t>
+          <t>2026-05-22 18:51:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1009,19 +1009,19 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>11833</v>
+      </c>
+      <c r="O8" t="n">
         <v>526</v>
-      </c>
-      <c r="O8" t="n">
-        <v>131</v>
       </c>
       <c r="P8" t="n">
         <v>263</v>
       </c>
       <c r="Q8" t="n">
+        <v>131</v>
+      </c>
+      <c r="R8" t="n">
         <v>526</v>
-      </c>
-      <c r="R8" t="n">
-        <v>11833</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-22 18:27:08</t>
+          <t>2026-05-22 18:51:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>50</v>
+        <v>624</v>
       </c>
       <c r="O9" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="P9" t="n">
         <v>7</v>
       </c>
       <c r="Q9" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="R9" t="n">
-        <v>624</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-22 18:27:10</t>
+          <t>2026-05-22 18:51:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,19 +1153,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>224</v>
+        <v>650</v>
       </c>
       <c r="O10" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="P10" t="n">
         <v>41</v>
       </c>
       <c r="Q10" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="R10" t="n">
-        <v>650</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-22 18:27:11</t>
+          <t>2026-05-22 18:51:44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1225,19 +1225,19 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>11</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>13</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-22 18:27:13</t>
+          <t>2026-05-22 18:51:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1297,19 +1297,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>85</v>
+        <v>2505</v>
       </c>
       <c r="O12" t="n">
-        <v>28</v>
+        <v>142</v>
       </c>
       <c r="P12" t="n">
         <v>57</v>
       </c>
       <c r="Q12" t="n">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="R12" t="n">
-        <v>2505</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-22 18:27:15</t>
+          <t>2026-05-22 18:51:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1369,19 +1369,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>98</v>
+        <v>357</v>
       </c>
       <c r="O13" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="P13" t="n">
         <v>16</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="R13" t="n">
-        <v>357</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-22 18:27:16</t>
+          <t>2026-05-22 18:51:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1441,19 +1441,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
         <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>145</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-22 18:27:17</t>
+          <t>2026-05-22 18:51:50</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1525,7 +1525,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-22 18:27:19</t>
+          <t>2026-05-22 18:51:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>27663</v>
+      </c>
+      <c r="O16" t="n">
         <v>1243</v>
-      </c>
-      <c r="O16" t="n">
-        <v>311</v>
       </c>
       <c r="P16" t="n">
         <v>622</v>
       </c>
       <c r="Q16" t="n">
+        <v>311</v>
+      </c>
+      <c r="R16" t="n">
         <v>1243</v>
-      </c>
-      <c r="R16" t="n">
-        <v>27663</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:31</t>
+          <t>2026-05-23 17:51:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:32</t>
+          <t>2026-05-23 17:51:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:34</t>
+          <t>2026-05-23 17:51:31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:35</t>
+          <t>2026-05-23 17:51:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:37</t>
+          <t>2026-05-23 17:51:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:38</t>
+          <t>2026-05-23 17:51:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:40</t>
+          <t>2026-05-23 17:51:36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:41</t>
+          <t>2026-05-23 17:51:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:43</t>
+          <t>2026-05-23 17:51:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:44</t>
+          <t>2026-05-23 17:51:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:46</t>
+          <t>2026-05-23 17:51:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:47</t>
+          <t>2026-05-23 17:51:44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:48</t>
+          <t>2026-05-23 17:51:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:50</t>
+          <t>2026-05-23 17:51:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:51</t>
+          <t>2026-05-23 17:51:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>27663</v>
+        <v>27974</v>
       </c>
       <c r="O16" t="n">
         <v>1243</v>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:28</t>
+          <t>2026-05-24 17:48:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:29</t>
+          <t>2026-05-24 17:48:33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81974</v>
+        <v>4.81951</v>
       </c>
       <c r="G3" t="n">
-        <v>12399</v>
+        <v>12405</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11531</v>
+        <v>11537</v>
       </c>
       <c r="O3" t="n">
         <v>248</v>
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:31</t>
+          <t>2026-05-24 17:48:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.88561</v>
+        <v>3.88584</v>
       </c>
       <c r="G4" t="n">
-        <v>4773</v>
+        <v>4774</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="O4" t="n">
         <v>382</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:32</t>
+          <t>2026-05-24 17:48:36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.53619</v>
+        <v>2.53555</v>
       </c>
       <c r="G5" t="n">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="O5" t="n">
         <v>96</v>
@@ -805,7 +805,7 @@
         <v>144</v>
       </c>
       <c r="R5" t="n">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:34</t>
+          <t>2026-05-24 17:48:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:35</t>
+          <t>2026-05-24 17:48:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:36</t>
+          <t>2026-05-24 17:48:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74855</v>
+        <v>4.74798</v>
       </c>
       <c r="G8" t="n">
-        <v>13148</v>
+        <v>13150</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,19 +1009,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>11833</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>263</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>526</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:38</t>
+          <t>2026-05-24 17:48:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>624</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:39</t>
+          <t>2026-05-24 17:48:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.86122</v>
+        <v>3.86234</v>
       </c>
       <c r="G10" t="n">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1153,19 +1153,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:41</t>
+          <t>2026-05-24 17:48:44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:42</t>
+          <t>2026-05-24 17:48:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74535</v>
+        <v>4.74439</v>
       </c>
       <c r="G12" t="n">
-        <v>2847</v>
+        <v>2852</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,19 +1297,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2505</v>
+        <v>2510</v>
       </c>
       <c r="O12" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P12" t="n">
         <v>57</v>
       </c>
       <c r="Q12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:44</t>
+          <t>2026-05-24 17:48:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:45</t>
+          <t>2026-05-24 17:48:47</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1441,19 +1441,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:46</t>
+          <t>2026-05-24 17:48:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:48</t>
+          <t>2026-05-24 17:48:50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.75005</v>
+        <v>4.75047</v>
       </c>
       <c r="G16" t="n">
-        <v>31082</v>
+        <v>31115</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>27974</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1243</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>622</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1243</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:31</t>
+          <t>2026-05-25 15:37:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:33</t>
+          <t>2026-05-25 15:37:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81951</v>
+        <v>4.81938</v>
       </c>
       <c r="G3" t="n">
-        <v>12405</v>
+        <v>12413</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11537</v>
+        <v>11544</v>
       </c>
       <c r="O3" t="n">
         <v>248</v>
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:34</t>
+          <t>2026-05-25 15:37:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:36</t>
+          <t>2026-05-25 15:37:14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.53555</v>
+        <v>2.53364</v>
       </c>
       <c r="G5" t="n">
-        <v>2405</v>
+        <v>2408</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="O5" t="n">
         <v>96</v>
@@ -805,7 +805,7 @@
         <v>144</v>
       </c>
       <c r="R5" t="n">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:37</t>
+          <t>2026-05-25 15:37:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:39</t>
+          <t>2026-05-25 15:37:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.01959</v>
+        <v>4.01987</v>
       </c>
       <c r="G7" t="n">
-        <v>3623</v>
+        <v>3624</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:40</t>
+          <t>2026-05-25 15:37:22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74798</v>
+        <v>4.74842</v>
       </c>
       <c r="G8" t="n">
-        <v>13150</v>
+        <v>13161</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,19 +1009,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>11845</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>526</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>526</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:41</t>
+          <t>2026-05-25 15:37:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>5.0.9</t>
+          <t>5.1.0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1077,23 +1077,23 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>April 07, 2026</t>
+          <t>May 24, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>624</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:42</t>
+          <t>2026-05-25 15:37:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.86234</v>
+        <v>3.85953</v>
       </c>
       <c r="G10" t="n">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.1.24</t>
+          <t>2.1.25</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1149,23 +1149,23 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>May 06, 2026</t>
+          <t>May 24, 2026</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>652</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:44</t>
+          <t>2026-05-25 15:37:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:45</t>
+          <t>2026-05-25 15:37:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74439</v>
+        <v>4.74231</v>
       </c>
       <c r="G12" t="n">
-        <v>2852</v>
+        <v>2860</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2510</v>
+        <v>2517</v>
       </c>
       <c r="O12" t="n">
         <v>143</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:46</t>
+          <t>2026-05-25 15:37:34</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.02123</v>
+        <v>4.02311</v>
       </c>
       <c r="G13" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O13" t="n">
         <v>26</v>
@@ -1381,7 +1381,7 @@
         <v>21</v>
       </c>
       <c r="R13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:47</t>
+          <t>2026-05-25 15:37:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1441,19 +1441,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:49</t>
+          <t>2026-05-25 15:37:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:50</t>
+          <t>2026-05-25 15:37:41</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.75047</v>
+        <v>4.75028</v>
       </c>
       <c r="G16" t="n">
-        <v>31115</v>
+        <v>31139</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.0.2</t>
+          <t>3.1.0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1581,23 +1581,23 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>January 21, 2026</t>
+          <t>May 24, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>27714</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>623</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:06</t>
+          <t>2026-05-25 18:20:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:09</t>
+          <t>2026-05-25 18:20:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81938</v>
+        <v>4.81869</v>
       </c>
       <c r="G3" t="n">
-        <v>12413</v>
+        <v>12426</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11544</v>
+        <v>11556</v>
       </c>
       <c r="O3" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P3" t="n">
         <v>124</v>
@@ -661,7 +661,7 @@
         <v>124</v>
       </c>
       <c r="R3" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:11</t>
+          <t>2026-05-25 18:20:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.88584</v>
+        <v>3.884</v>
       </c>
       <c r="G4" t="n">
-        <v>4774</v>
+        <v>4776</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2960</v>
+        <v>2961</v>
       </c>
       <c r="O4" t="n">
         <v>382</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:14</t>
+          <t>2026-05-25 18:21:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.53364</v>
+        <v>2.53297</v>
       </c>
       <c r="G5" t="n">
-        <v>2408</v>
+        <v>2411</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="O5" t="n">
         <v>96</v>
@@ -802,10 +802,10 @@
         <v>96</v>
       </c>
       <c r="Q5" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="R5" t="n">
-        <v>1300</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:16</t>
+          <t>2026-05-25 18:21:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:19</t>
+          <t>2026-05-25 18:21:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.01987</v>
+        <v>4.01959</v>
       </c>
       <c r="G7" t="n">
-        <v>3624</v>
+        <v>3625</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="O7" t="n">
         <v>399</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:22</t>
+          <t>2026-05-25 18:21:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74842</v>
+        <v>4.74833</v>
       </c>
       <c r="G8" t="n">
-        <v>13161</v>
+        <v>13176</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,19 +1009,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>11845</v>
+        <v>11858</v>
       </c>
       <c r="O8" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="P8" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q8" t="n">
         <v>132</v>
       </c>
       <c r="R8" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:24</t>
+          <t>2026-05-25 18:21:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:27</t>
+          <t>2026-05-25 18:21:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:29</t>
+          <t>2026-05-25 18:21:14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:32</t>
+          <t>2026-05-25 18:21:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:34</t>
+          <t>2026-05-25 18:21:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:37</t>
+          <t>2026-05-25 18:21:22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:39</t>
+          <t>2026-05-25 18:21:24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:41</t>
+          <t>2026-05-25 18:21:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.75028</v>
+        <v>4.74998</v>
       </c>
       <c r="G16" t="n">
-        <v>31139</v>
+        <v>31174</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>27714</v>
+        <v>27745</v>
       </c>
       <c r="O16" t="n">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="P16" t="n">
         <v>623</v>
       </c>
       <c r="Q16" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="R16" t="n">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-25 18:20:52</t>
+          <t>2026-05-26 19:12:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-25 18:20:55</t>
+          <t>2026-05-26 19:12:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81869</v>
+        <v>4.81877</v>
       </c>
       <c r="G3" t="n">
-        <v>12426</v>
+        <v>12432</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11556</v>
+        <v>11562</v>
       </c>
       <c r="O3" t="n">
         <v>249</v>
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-25 18:20:57</t>
+          <t>2026-05-26 19:12:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-25 18:21:00</t>
+          <t>2026-05-26 19:12:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.53297</v>
+        <v>2.53043</v>
       </c>
       <c r="G5" t="n">
-        <v>2411</v>
+        <v>2415</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="O5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q5" t="n">
         <v>145</v>
       </c>
       <c r="R5" t="n">
-        <v>1302</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-25 18:21:02</t>
+          <t>2026-05-26 19:12:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-25 18:21:05</t>
+          <t>2026-05-26 19:12:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.01959</v>
+        <v>4.02013</v>
       </c>
       <c r="G7" t="n">
-        <v>3625</v>
+        <v>3627</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="O7" t="n">
         <v>399</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-25 18:21:07</t>
+          <t>2026-05-26 19:12:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74833</v>
+        <v>4.74917</v>
       </c>
       <c r="G8" t="n">
-        <v>13176</v>
+        <v>13192</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>11858</v>
+        <v>11873</v>
       </c>
       <c r="O8" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P8" t="n">
         <v>264</v>
@@ -1021,7 +1021,7 @@
         <v>132</v>
       </c>
       <c r="R8" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-25 18:21:10</t>
+          <t>2026-05-26 19:12:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-25 18:21:12</t>
+          <t>2026-05-26 19:12:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-25 18:21:14</t>
+          <t>2026-05-26 19:12:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-25 18:21:17</t>
+          <t>2026-05-26 19:12:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74231</v>
+        <v>4.74275</v>
       </c>
       <c r="G12" t="n">
-        <v>2860</v>
+        <v>2865</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2517</v>
+        <v>2521</v>
       </c>
       <c r="O12" t="n">
         <v>143</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-25 18:21:19</t>
+          <t>2026-05-26 19:12:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-25 18:21:22</t>
+          <t>2026-05-26 19:12:44</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-25 18:21:24</t>
+          <t>2026-05-26 19:12:47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-25 18:21:26</t>
+          <t>2026-05-26 19:12:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74998</v>
+        <v>4.75013</v>
       </c>
       <c r="G16" t="n">
-        <v>31174</v>
+        <v>31200</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.1.0</t>
+          <t>3.1.1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1581,23 +1581,23 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>May 24, 2026</t>
+          <t>May 25, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>27745</v>
+        <v>28080</v>
       </c>
       <c r="O16" t="n">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="P16" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="Q16" t="n">
         <v>312</v>
       </c>
       <c r="R16" t="n">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:15</t>
+          <t>2026-05-27 19:11:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:18</t>
+          <t>2026-05-27 19:11:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81877</v>
+        <v>4.81827</v>
       </c>
       <c r="G3" t="n">
-        <v>12432</v>
+        <v>12442</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11562</v>
+        <v>11571</v>
       </c>
       <c r="O3" t="n">
         <v>249</v>
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:20</t>
+          <t>2026-05-27 19:12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.884</v>
+        <v>3.88377</v>
       </c>
       <c r="G4" t="n">
-        <v>4776</v>
+        <v>4775</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="O4" t="n">
         <v>382</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:23</t>
+          <t>2026-05-27 19:12:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.53043</v>
+        <v>2.53142</v>
       </c>
       <c r="G5" t="n">
-        <v>2415</v>
+        <v>2418</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="O5" t="n">
         <v>97</v>
@@ -805,7 +805,7 @@
         <v>145</v>
       </c>
       <c r="R5" t="n">
-        <v>1304</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:25</t>
+          <t>2026-05-27 19:12:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:28</t>
+          <t>2026-05-27 19:12:06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.02013</v>
+        <v>4.019</v>
       </c>
       <c r="G7" t="n">
-        <v>3627</v>
+        <v>3631</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2321</v>
+        <v>2324</v>
       </c>
       <c r="O7" t="n">
         <v>399</v>
       </c>
       <c r="P7" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q7" t="n">
         <v>145</v>
       </c>
       <c r="R7" t="n">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:30</t>
+          <t>2026-05-27 19:12:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74917</v>
+        <v>4.74888</v>
       </c>
       <c r="G8" t="n">
-        <v>13192</v>
+        <v>13201</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>11873</v>
+        <v>11881</v>
       </c>
       <c r="O8" t="n">
         <v>528</v>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:32</t>
+          <t>2026-05-27 19:12:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:35</t>
+          <t>2026-05-27 19:12:14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:37</t>
+          <t>2026-05-27 19:12:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:40</t>
+          <t>2026-05-27 19:12:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74275</v>
+        <v>4.74321</v>
       </c>
       <c r="G12" t="n">
-        <v>2865</v>
+        <v>2870</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2521</v>
+        <v>2526</v>
       </c>
       <c r="O12" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P12" t="n">
         <v>57</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:42</t>
+          <t>2026-05-27 19:12:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.02311</v>
+        <v>4.01731</v>
       </c>
       <c r="G13" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O13" t="n">
         <v>26</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:44</t>
+          <t>2026-05-27 19:12:23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:47</t>
+          <t>2026-05-27 19:12:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:49</t>
+          <t>2026-05-27 19:12:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.75013</v>
+        <v>4.74999</v>
       </c>
       <c r="G16" t="n">
-        <v>31200</v>
+        <v>31215</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>28080</v>
+        <v>27781</v>
       </c>
       <c r="O16" t="n">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="P16" t="n">
         <v>624</v>
@@ -1597,7 +1597,7 @@
         <v>312</v>
       </c>
       <c r="R16" t="n">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-27 19:11:55</t>
+          <t>2026-05-28 19:32:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-27 19:11:57</t>
+          <t>2026-05-28 19:32:23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81827</v>
+        <v>4.81803</v>
       </c>
       <c r="G3" t="n">
-        <v>12442</v>
+        <v>12447</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11571</v>
+        <v>11576</v>
       </c>
       <c r="O3" t="n">
         <v>249</v>
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-27 19:12:00</t>
+          <t>2026-05-28 19:32:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-27 19:12:02</t>
+          <t>2026-05-28 19:32:27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.53142</v>
+        <v>2.52893</v>
       </c>
       <c r="G5" t="n">
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>145</v>
       </c>
       <c r="R5" t="n">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-27 19:12:04</t>
+          <t>2026-05-28 19:32:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-27 19:12:06</t>
+          <t>2026-05-28 19:32:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-27 19:12:09</t>
+          <t>2026-05-28 19:32:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74888</v>
+        <v>4.7493</v>
       </c>
       <c r="G8" t="n">
-        <v>13201</v>
+        <v>13207</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>11881</v>
+        <v>11886</v>
       </c>
       <c r="O8" t="n">
         <v>528</v>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-27 19:12:11</t>
+          <t>2026-05-28 19:32:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-27 19:12:14</t>
+          <t>2026-05-28 19:32:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-27 19:12:16</t>
+          <t>2026-05-28 19:32:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-27 19:12:18</t>
+          <t>2026-05-28 19:32:44</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.74321</v>
+        <v>4.74338</v>
       </c>
       <c r="G12" t="n">
-        <v>2870</v>
+        <v>2872</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="O12" t="n">
         <v>144</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-27 19:12:21</t>
+          <t>2026-05-28 19:32:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-27 19:12:23</t>
+          <t>2026-05-28 19:32:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-27 19:12:25</t>
+          <t>2026-05-28 19:32:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-27 19:12:28</t>
+          <t>2026-05-28 19:32:54</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.74999</v>
+        <v>4.75012</v>
       </c>
       <c r="G16" t="n">
-        <v>31215</v>
+        <v>31219</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>27781</v>
+        <v>27785</v>
       </c>
       <c r="O16" t="n">
         <v>1249</v>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:20</t>
+          <t>2026-05-29 19:25:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:23</t>
+          <t>2026-05-29 19:25:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81803</v>
+        <v>4.81812</v>
       </c>
       <c r="G3" t="n">
-        <v>12447</v>
+        <v>12453</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11576</v>
+        <v>11581</v>
       </c>
       <c r="O3" t="n">
         <v>249</v>
       </c>
       <c r="P3" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q3" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R3" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:25</t>
+          <t>2026-05-29 19:25:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:27</t>
+          <t>2026-05-29 19:25:50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.52893</v>
+        <v>2.52972</v>
       </c>
       <c r="G5" t="n">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="O5" t="n">
         <v>97</v>
@@ -805,7 +805,7 @@
         <v>145</v>
       </c>
       <c r="R5" t="n">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="6">
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:30</t>
+          <t>2026-05-29 19:25:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:32</t>
+          <t>2026-05-29 19:25:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.019</v>
+        <v>4.01872</v>
       </c>
       <c r="G7" t="n">
-        <v>3631</v>
+        <v>3630</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="O7" t="n">
         <v>399</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:35</t>
+          <t>2026-05-29 19:25:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.7493</v>
+        <v>4.74938</v>
       </c>
       <c r="G8" t="n">
-        <v>13207</v>
+        <v>13211</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>11886</v>
+        <v>11890</v>
       </c>
       <c r="O8" t="n">
         <v>528</v>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:37</t>
+          <t>2026-05-29 19:25:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:40</t>
+          <t>2026-05-29 19:26:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:42</t>
+          <t>2026-05-29 19:26:04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:44</t>
+          <t>2026-05-29 19:26:06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:47</t>
+          <t>2026-05-29 19:26:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:49</t>
+          <t>2026-05-29 19:26:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:51</t>
+          <t>2026-05-29 19:26:13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:54</t>
+          <t>2026-05-29 19:26:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.75012</v>
+        <v>4.75014</v>
       </c>
       <c r="G16" t="n">
-        <v>31219</v>
+        <v>31223</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>27785</v>
+        <v>28101</v>
       </c>
       <c r="O16" t="n">
         <v>1249</v>

--- a/data/Jordan_banks_Reviews_AppleStore.xlsx
+++ b/data/Jordan_banks_Reviews_AppleStore.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:43</t>
+          <t>2026-05-30 17:54:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:45</t>
+          <t>2026-05-30 17:55:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.81812</v>
+        <v>4.81816</v>
       </c>
       <c r="G3" t="n">
-        <v>12453</v>
+        <v>12456</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11581</v>
+        <v>11584</v>
       </c>
       <c r="O3" t="n">
         <v>249</v>
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:48</t>
+          <t>2026-05-30 17:55:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:50</t>
+          <t>2026-05-30 17:55:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.52972</v>
+        <v>2.53074</v>
       </c>
       <c r="G5" t="n">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:53</t>
+          <t>2026-05-30 17:55:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:55</t>
+          <t>2026-05-30 17:55:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.01872</v>
+        <v>4.019</v>
       </c>
       <c r="G7" t="n">
-        <v>3630</v>
+        <v>3631</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="O7" t="n">
         <v>399</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:57</t>
+          <t>2026-05-30 17:55:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.74938</v>
+        <v>4.74974</v>
       </c>
       <c r="G8" t="n">
-        <v>13211</v>
+        <v>13215</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>11890</v>
+        <v>11894</v>
       </c>
       <c r="O8" t="n">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P8" t="n">
         <v>264</v>
@@ -1021,7 +1021,7 @@
         <v>132</v>
       </c>
       <c r="R8" t="n">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:59</t>
+          <t>2026-05-30 17:55:14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>5.1.0</t>
+          <t>5.1.1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>May 24, 2026</t>
+          <t>May 30, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-29 19:26:02</t>
+          <t>2026-05-30 17:55:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-29 19:26:04</t>
+          <t>2026-05-30 17:55:18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-29 19:26:06</t>
+          <t>2026-05-30 17:55:20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-29 19:26:08</t>
+          <t>2026-05-30 17:55:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-29 19:26:10</t>
+          <t>2026-05-30 17:55:25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-29 19:26:13</t>
+          <t>2026-05-30 17:55:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-29 19:26:15</t>
+          <t>2026-05-30 17:55:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.75014</v>
+        <v>4.75028</v>
       </c>
       <c r="G16" t="n">
-        <v>31223</v>
+        <v>31224</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>28101</v>
+        <v>28102</v>
       </c>
       <c r="O16" t="n">
         <v>1249</v>
